--- a/Data/IJ_Config.xlsx
+++ b/Data/IJ_Config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Documents\UiPath\IJ_WysylanieFaktur\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5991767-CE53-4180-AE9F-23A1E9D6BE43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A12F85B9-6A70-49A2-9EDE-CB3DE7B6034E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="55">
   <si>
     <t>Name</t>
   </si>
@@ -175,6 +175,18 @@
   </si>
   <si>
     <t>NUMER FAKTURY</t>
+  </si>
+  <si>
+    <t>URL</t>
+  </si>
+  <si>
+    <t>https://funnyjudowarszawa.fakturownia.pl</t>
+  </si>
+  <si>
+    <t>ColumnKontakt</t>
+  </si>
+  <si>
+    <t>KONTAKT</t>
   </si>
 </sst>
 </file>
@@ -540,7 +552,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z994"/>
+  <dimension ref="A1:Z995"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="43.5703125" customWidth="1"/>
@@ -639,9 +651,23 @@
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="1:26" ht="14.25" customHeight="1"/>
+    <row r="9" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A9" t="s">
+        <v>53</v>
+      </c>
+      <c r="B9" t="s">
+        <v>54</v>
+      </c>
+    </row>
     <row r="10" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="11" spans="1:26" ht="14.25" customHeight="1"/>
+    <row r="11" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A11" t="s">
+        <v>51</v>
+      </c>
+      <c r="B11" t="s">
+        <v>52</v>
+      </c>
+    </row>
     <row r="12" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="13" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="14" spans="1:26" ht="14.25" customHeight="1"/>
@@ -1625,6 +1651,7 @@
     <row r="992" ht="14.25" customHeight="1"/>
     <row r="993" ht="14.25" customHeight="1"/>
     <row r="994" ht="14.25" customHeight="1"/>
+    <row r="995" ht="14.25" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Data/IJ_Config.xlsx
+++ b/Data/IJ_Config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Documents\UiPath\IJ_WysylanieFaktur\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A12F85B9-6A70-49A2-9EDE-CB3DE7B6034E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B555D5C-28D6-4E6A-9CC4-30FB2E5DF716}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="57">
   <si>
     <t>Name</t>
   </si>
@@ -150,9 +150,6 @@
     <t>Range</t>
   </si>
   <si>
-    <t>I:N</t>
-  </si>
-  <si>
     <t>DANE DO FAKTURY</t>
   </si>
   <si>
@@ -187,6 +184,15 @@
   </si>
   <si>
     <t>KONTAKT</t>
+  </si>
+  <si>
+    <t>E:N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      numer ▼   </t>
+  </si>
+  <si>
+    <t>ColumnSortBy</t>
   </si>
 </sst>
 </file>
@@ -616,59 +622,66 @@
         <v>41</v>
       </c>
       <c r="B4" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:26" ht="14.25" customHeight="1">
       <c r="A5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:26" ht="14.25" customHeight="1">
       <c r="A6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B6" t="s">
         <v>45</v>
-      </c>
-      <c r="B6" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:26" ht="14.25" customHeight="1">
       <c r="A7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B7" t="s">
         <v>47</v>
-      </c>
-      <c r="B7" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1">
       <c r="A8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8" t="s">
         <v>49</v>
-      </c>
-      <c r="B8" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:26" ht="14.25" customHeight="1">
       <c r="A9" t="s">
+        <v>52</v>
+      </c>
+      <c r="B9" t="s">
         <v>53</v>
-      </c>
-      <c r="B9" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="10" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="11" spans="1:26" ht="14.25" customHeight="1">
       <c r="A11" t="s">
+        <v>50</v>
+      </c>
+      <c r="B11" t="s">
         <v>51</v>
       </c>
-      <c r="B11" t="s">
-        <v>52</v>
-      </c>
     </row>
-    <row r="12" spans="1:26" ht="14.25" customHeight="1"/>
+    <row r="12" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A12" t="s">
+        <v>56</v>
+      </c>
+      <c r="B12" t="s">
+        <v>55</v>
+      </c>
+    </row>
     <row r="13" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="14" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="15" spans="1:26" ht="14.25" customHeight="1"/>

--- a/Data/IJ_Config.xlsx
+++ b/Data/IJ_Config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Documents\UiPath\IJ_WysylanieFaktur\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B555D5C-28D6-4E6A-9CC4-30FB2E5DF716}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EEC730F-B241-45E3-A782-0406821D0A96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="77">
   <si>
     <t>Name</t>
   </si>
@@ -177,22 +177,82 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://funnyjudowarszawa.fakturownia.pl</t>
-  </si>
-  <si>
     <t>ColumnKontakt</t>
   </si>
   <si>
     <t>KONTAKT</t>
   </si>
   <si>
-    <t>E:N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">      numer ▼   </t>
-  </si>
-  <si>
     <t>ColumnSortBy</t>
+  </si>
+  <si>
+    <t>Suffix</t>
+  </si>
+  <si>
+    <t>NumerRegex</t>
+  </si>
+  <si>
+    <t>/FUN</t>
+  </si>
+  <si>
+    <t>^\d{2,4}</t>
+  </si>
+  <si>
+    <t>ILOŚĆ LICZONYCH DO FAKTURY/PŁACĄCYCH SKŁADKĘ</t>
+  </si>
+  <si>
+    <t>NAZWA USŁUGI</t>
+  </si>
+  <si>
+    <t>ColumnNazwaUslugi</t>
+  </si>
+  <si>
+    <t>ColumnIlosc</t>
+  </si>
+  <si>
+    <t>Months</t>
+  </si>
+  <si>
+    <t>sty,lut,mar,kwi,maj,cze,lip,sie,wrz,paź,lis,gru</t>
+  </si>
+  <si>
+    <t>MonthsRegex</t>
+  </si>
+  <si>
+    <t>NUMER ▼</t>
+  </si>
+  <si>
+    <t>ColumnIloscOsob</t>
+  </si>
+  <si>
+    <t>ILOŚĆ</t>
+  </si>
+  <si>
+    <t>ColumnIloscGrup</t>
+  </si>
+  <si>
+    <t>ILOŚĆ GRUP ODBYTYCH</t>
+  </si>
+  <si>
+    <t>OsobyRegex</t>
+  </si>
+  <si>
+    <t>\d+(?= ?grup)</t>
+  </si>
+  <si>
+    <t>E:Q</t>
+  </si>
+  <si>
+    <t>GrupyRegex</t>
+  </si>
+  <si>
+    <t>(?:sty|lut|mar|kwi|maj|cze|lip|sie|wrz|paź|lis|grud).*?\b</t>
+  </si>
+  <si>
+    <t>\d+,?\d+(?= ?os\.?)</t>
+  </si>
+  <si>
+    <t>https://funnyjudowarszawa.fakturownia.pl/invoices</t>
   </si>
 </sst>
 </file>
@@ -558,11 +618,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z995"/>
+  <dimension ref="A1:Z998"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="43.5703125" customWidth="1"/>
-    <col min="2" max="2" width="43" customWidth="1"/>
+    <col min="2" max="2" width="77.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="81.42578125" customWidth="1"/>
     <col min="4" max="26" width="8.7109375" customWidth="1"/>
   </cols>
@@ -622,7 +682,7 @@
         <v>41</v>
       </c>
       <c r="B4" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:26" ht="14.25" customHeight="1">
@@ -643,65 +703,135 @@
     </row>
     <row r="7" spans="1:26" ht="14.25" customHeight="1">
       <c r="A7" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="B7" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1">
       <c r="A8" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B8" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:26" ht="14.25" customHeight="1">
       <c r="A9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B9" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A10" t="s">
+        <v>51</v>
+      </c>
+      <c r="B10" t="s">
         <v>52</v>
       </c>
-      <c r="B9" t="s">
-        <v>53</v>
-      </c>
     </row>
-    <row r="10" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="11" spans="1:26" ht="14.25" customHeight="1">
       <c r="A11" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="B11" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12" spans="1:26" ht="14.25" customHeight="1">
       <c r="A12" t="s">
+        <v>61</v>
+      </c>
+      <c r="B12" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A13" t="s">
+        <v>66</v>
+      </c>
+      <c r="B13" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A14" t="s">
+        <v>68</v>
+      </c>
+      <c r="B14" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A15" t="s">
+        <v>50</v>
+      </c>
+      <c r="B15" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A16" t="s">
+        <v>53</v>
+      </c>
+      <c r="B16" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A17" t="s">
+        <v>54</v>
+      </c>
+      <c r="B17" t="s">
         <v>56</v>
       </c>
-      <c r="B12" t="s">
-        <v>55</v>
-      </c>
     </row>
-    <row r="13" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="14" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="15" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="16" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="17" ht="14.25" customHeight="1"/>
-    <row r="18" ht="14.25" customHeight="1"/>
-    <row r="19" ht="14.25" customHeight="1"/>
-    <row r="20" ht="14.25" customHeight="1"/>
-    <row r="21" ht="14.25" customHeight="1"/>
-    <row r="22" ht="14.25" customHeight="1"/>
-    <row r="23" ht="14.25" customHeight="1"/>
-    <row r="24" ht="14.25" customHeight="1"/>
-    <row r="25" ht="14.25" customHeight="1"/>
-    <row r="26" ht="14.25" customHeight="1"/>
-    <row r="27" ht="14.25" customHeight="1"/>
-    <row r="28" ht="14.25" customHeight="1"/>
-    <row r="29" ht="14.25" customHeight="1"/>
-    <row r="30" ht="14.25" customHeight="1"/>
-    <row r="31" ht="14.25" customHeight="1"/>
-    <row r="32" ht="14.25" customHeight="1"/>
+    <row r="18" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A18" t="s">
+        <v>62</v>
+      </c>
+      <c r="B18" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A19" t="s">
+        <v>64</v>
+      </c>
+      <c r="B19" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A20" t="s">
+        <v>73</v>
+      </c>
+      <c r="B20" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A21" t="s">
+        <v>70</v>
+      </c>
+      <c r="B21" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="23" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="24" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="25" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="26" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="27" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="28" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="29" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="30" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="31" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="32" spans="1:2" ht="14.25" customHeight="1"/>
     <row r="33" ht="14.25" customHeight="1"/>
     <row r="34" ht="14.25" customHeight="1"/>
     <row r="35" ht="14.25" customHeight="1"/>
@@ -1665,6 +1795,9 @@
     <row r="993" ht="14.25" customHeight="1"/>
     <row r="994" ht="14.25" customHeight="1"/>
     <row r="995" ht="14.25" customHeight="1"/>
+    <row r="996" ht="14.25" customHeight="1"/>
+    <row r="997" ht="14.25" customHeight="1"/>
+    <row r="998" ht="14.25" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Data/IJ_Config.xlsx
+++ b/Data/IJ_Config.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Documents\UiPath\IJ_WysylanieFaktur\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EEC730F-B241-45E3-A782-0406821D0A96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47EA378B-7C00-4A4F-AEED-DC9F3F81A048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="75">
   <si>
     <t>Name</t>
   </si>
@@ -210,12 +210,6 @@
     <t>ColumnIlosc</t>
   </si>
   <si>
-    <t>Months</t>
-  </si>
-  <si>
-    <t>sty,lut,mar,kwi,maj,cze,lip,sie,wrz,paź,lis,gru</t>
-  </si>
-  <si>
     <t>MonthsRegex</t>
   </si>
   <si>
@@ -237,9 +231,6 @@
     <t>OsobyRegex</t>
   </si>
   <si>
-    <t>\d+(?= ?grup)</t>
-  </si>
-  <si>
     <t>E:Q</t>
   </si>
   <si>
@@ -249,10 +240,13 @@
     <t>(?:sty|lut|mar|kwi|maj|cze|lip|sie|wrz|paź|lis|grud).*?\b</t>
   </si>
   <si>
-    <t>\d+,?\d+(?= ?os\.?)</t>
-  </si>
-  <si>
     <t>https://funnyjudowarszawa.fakturownia.pl/invoices</t>
+  </si>
+  <si>
+    <t>\d+(?= ?grup)|\d+(?= ?zaj\.)</t>
+  </si>
+  <si>
+    <t>(?:\d+,)?\d+(?= ?os\.?)</t>
   </si>
 </sst>
 </file>
@@ -618,7 +612,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z998"/>
+  <dimension ref="A1:Z997"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="43.5703125" customWidth="1"/>
@@ -682,7 +676,7 @@
         <v>41</v>
       </c>
       <c r="B4" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5" spans="1:26" ht="14.25" customHeight="1">
@@ -746,12 +740,12 @@
         <v>61</v>
       </c>
       <c r="B12" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13" spans="1:26" ht="14.25" customHeight="1">
       <c r="A13" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B13" t="s">
         <v>58</v>
@@ -759,10 +753,10 @@
     </row>
     <row r="14" spans="1:26" ht="14.25" customHeight="1">
       <c r="A14" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B14" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="15" spans="1:26" ht="14.25" customHeight="1">
@@ -770,7 +764,7 @@
         <v>50</v>
       </c>
       <c r="B15" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16" spans="1:26" ht="14.25" customHeight="1">
@@ -778,7 +772,7 @@
         <v>53</v>
       </c>
       <c r="B16" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="14.25" customHeight="1">
@@ -794,33 +788,26 @@
         <v>62</v>
       </c>
       <c r="B18" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="14.25" customHeight="1">
       <c r="A19" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="B19" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="14.25" customHeight="1">
       <c r="A20" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="B20" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A21" t="s">
-        <v>70</v>
-      </c>
-      <c r="B21" t="s">
-        <v>75</v>
-      </c>
-    </row>
+    <row r="21" spans="1:2" ht="14.25" customHeight="1"/>
     <row r="22" spans="1:2" ht="14.25" customHeight="1"/>
     <row r="23" spans="1:2" ht="14.25" customHeight="1"/>
     <row r="24" spans="1:2" ht="14.25" customHeight="1"/>
@@ -1797,7 +1784,6 @@
     <row r="995" ht="14.25" customHeight="1"/>
     <row r="996" ht="14.25" customHeight="1"/>
     <row r="997" ht="14.25" customHeight="1"/>
-    <row r="998" ht="14.25" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Data/IJ_Config.xlsx
+++ b/Data/IJ_Config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Documents\UiPath\IJ_WysylanieFaktur\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47EA378B-7C00-4A4F-AEED-DC9F3F81A048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD35273B-9872-4A2E-98B5-39466A00B01B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="74">
   <si>
     <t>Name</t>
   </si>
@@ -135,15 +135,9 @@
     <t xml:space="preserve">The maximum number of consecutive system exceptions was reached. </t>
   </si>
   <si>
-    <t>WorkbookAddress</t>
-  </si>
-  <si>
     <t>SheetName</t>
   </si>
   <si>
-    <t>C:\Users\Administrator\Downloads\EWIDENCJA I ROZLICZENIE - GRUDZIEŃ 2025.xlsx</t>
-  </si>
-  <si>
     <t>PLACÓWKI ROZLICZENIE</t>
   </si>
   <si>
@@ -240,13 +234,16 @@
     <t>(?:sty|lut|mar|kwi|maj|cze|lip|sie|wrz|paź|lis|grud).*?\b</t>
   </si>
   <si>
-    <t>https://funnyjudowarszawa.fakturownia.pl/invoices</t>
-  </si>
-  <si>
     <t>\d+(?= ?grup)|\d+(?= ?zaj\.)</t>
   </si>
   <si>
     <t>(?:\d+,)?\d+(?= ?os\.?)</t>
+  </si>
+  <si>
+    <t>Timeout</t>
+  </si>
+  <si>
+    <t>https://funnyjudoINSTANCJA.fakturownia.pl/invoices?kind=vat</t>
   </si>
 </sst>
 </file>
@@ -612,7 +609,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z997"/>
+  <dimension ref="A1:Z996"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="43.5703125" customWidth="1"/>
@@ -660,15 +657,15 @@
         <v>37</v>
       </c>
       <c r="B2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:26" ht="14.25" customHeight="1">
       <c r="A3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B3" t="s">
-        <v>40</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" spans="1:26" ht="14.25" customHeight="1">
@@ -676,31 +673,31 @@
         <v>41</v>
       </c>
       <c r="B4" t="s">
-        <v>69</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:26" ht="14.25" customHeight="1">
       <c r="A5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5" t="s">
         <v>43</v>
-      </c>
-      <c r="B5" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:26" ht="14.25" customHeight="1">
       <c r="A6" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="B6" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:26" ht="14.25" customHeight="1">
       <c r="A7" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="B7" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1">
@@ -713,34 +710,34 @@
     </row>
     <row r="9" spans="1:26" ht="14.25" customHeight="1">
       <c r="A9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:26" ht="14.25" customHeight="1">
       <c r="A10" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="B10" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11" spans="1:26" ht="14.25" customHeight="1">
       <c r="A11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B11" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="12" spans="1:26" ht="14.25" customHeight="1">
       <c r="A12" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B12" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13" spans="1:26" ht="14.25" customHeight="1">
@@ -748,63 +745,63 @@
         <v>64</v>
       </c>
       <c r="B13" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14" spans="1:26" ht="14.25" customHeight="1">
       <c r="A14" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="B14" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
     </row>
     <row r="15" spans="1:26" ht="14.25" customHeight="1">
       <c r="A15" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B15" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16" spans="1:26" ht="14.25" customHeight="1">
       <c r="A16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B16" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="14.25" customHeight="1">
       <c r="A17" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="B17" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="14.25" customHeight="1">
       <c r="A18" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="B18" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="14.25" customHeight="1">
       <c r="A19" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B19" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="14.25" customHeight="1">
       <c r="A20" t="s">
-        <v>68</v>
-      </c>
-      <c r="B20" t="s">
-        <v>74</v>
+        <v>72</v>
+      </c>
+      <c r="B20">
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="14.25" customHeight="1"/>
@@ -1783,7 +1780,6 @@
     <row r="994" ht="14.25" customHeight="1"/>
     <row r="995" ht="14.25" customHeight="1"/>
     <row r="996" ht="14.25" customHeight="1"/>
-    <row r="997" ht="14.25" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Data/IJ_Config.xlsx
+++ b/Data/IJ_Config.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Documents\UiPath\IJ_WysylanieFaktur\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD35273B-9872-4A2E-98B5-39466A00B01B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{927FBDE3-04B4-4D30-A260-2A7289CD9EC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -138,9 +138,6 @@
     <t>SheetName</t>
   </si>
   <si>
-    <t>PLACÓWKI ROZLICZENIE</t>
-  </si>
-  <si>
     <t>Range</t>
   </si>
   <si>
@@ -174,9 +171,6 @@
     <t>ColumnKontakt</t>
   </si>
   <si>
-    <t>KONTAKT</t>
-  </si>
-  <si>
     <t>ColumnSortBy</t>
   </si>
   <si>
@@ -195,9 +189,6 @@
     <t>ILOŚĆ LICZONYCH DO FAKTURY/PŁACĄCYCH SKŁADKĘ</t>
   </si>
   <si>
-    <t>NAZWA USŁUGI</t>
-  </si>
-  <si>
     <t>ColumnNazwaUslugi</t>
   </si>
   <si>
@@ -225,9 +216,6 @@
     <t>OsobyRegex</t>
   </si>
   <si>
-    <t>E:Q</t>
-  </si>
-  <si>
     <t>GrupyRegex</t>
   </si>
   <si>
@@ -244,6 +232,18 @@
   </si>
   <si>
     <t>https://funnyjudoINSTANCJA.fakturownia.pl/invoices?kind=vat</t>
+  </si>
+  <si>
+    <t>MAIL DO FAKTURY</t>
+  </si>
+  <si>
+    <t>NAZWA</t>
+  </si>
+  <si>
+    <t>F:O</t>
+  </si>
+  <si>
+    <t>Arkusz1</t>
   </si>
 </sst>
 </file>
@@ -657,148 +657,148 @@
         <v>37</v>
       </c>
       <c r="B2" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:26" ht="14.25" customHeight="1">
       <c r="A3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B3" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:26" ht="14.25" customHeight="1">
       <c r="A4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:26" ht="14.25" customHeight="1">
       <c r="A5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" t="s">
         <v>42</v>
-      </c>
-      <c r="B5" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:26" ht="14.25" customHeight="1">
       <c r="A6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B6" t="s">
         <v>53</v>
-      </c>
-      <c r="B6" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:26" ht="14.25" customHeight="1">
       <c r="A7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7" t="s">
         <v>44</v>
-      </c>
-      <c r="B7" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1">
       <c r="A8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B8" t="s">
         <v>46</v>
-      </c>
-      <c r="B8" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:26" ht="14.25" customHeight="1">
       <c r="A9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B9" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10" spans="1:26" ht="14.25" customHeight="1">
       <c r="A10" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B10" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11" spans="1:26" ht="14.25" customHeight="1">
       <c r="A11" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B11" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12" spans="1:26" ht="14.25" customHeight="1">
       <c r="A12" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B12" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" spans="1:26" ht="14.25" customHeight="1">
       <c r="A13" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B13" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14" spans="1:26" ht="14.25" customHeight="1">
       <c r="A14" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B14" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15" spans="1:26" ht="14.25" customHeight="1">
       <c r="A15" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B15" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="16" spans="1:26" ht="14.25" customHeight="1">
       <c r="A16" t="s">
+        <v>50</v>
+      </c>
+      <c r="B16" t="s">
         <v>52</v>
-      </c>
-      <c r="B16" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="14.25" customHeight="1">
       <c r="A17" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B17" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="14.25" customHeight="1">
       <c r="A18" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B18" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="14.25" customHeight="1">
       <c r="A19" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B19" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="14.25" customHeight="1">
       <c r="A20" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B20">
         <v>1</v>

--- a/Data/IJ_Config.xlsx
+++ b/Data/IJ_Config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Documents\UiPath\IJ_WysylanieFaktur\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{927FBDE3-04B4-4D30-A260-2A7289CD9EC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5FEEDCA-7381-4CAE-B4F5-FC6A058E5C58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -150,9 +150,6 @@
     <t>NIPRegex</t>
   </si>
   <si>
-    <t>\d[\d| |-]{7,13}\d</t>
-  </si>
-  <si>
     <t>ColumnKwota</t>
   </si>
   <si>
@@ -244,6 +241,9 @@
   </si>
   <si>
     <t>Arkusz1</t>
+  </si>
+  <si>
+    <t>\d[\d|-]{7,13}\d|\d[\d| ]{7,13}\d</t>
   </si>
 </sst>
 </file>
@@ -657,7 +657,7 @@
         <v>37</v>
       </c>
       <c r="B2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:26" ht="14.25" customHeight="1">
@@ -665,7 +665,7 @@
         <v>38</v>
       </c>
       <c r="B3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4" spans="1:26" ht="14.25" customHeight="1">
@@ -681,124 +681,124 @@
         <v>41</v>
       </c>
       <c r="B5" t="s">
-        <v>42</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:26" ht="14.25" customHeight="1">
       <c r="A6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:26" ht="14.25" customHeight="1">
       <c r="A7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7" t="s">
         <v>43</v>
-      </c>
-      <c r="B7" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1">
       <c r="A8" t="s">
+        <v>44</v>
+      </c>
+      <c r="B8" t="s">
         <v>45</v>
-      </c>
-      <c r="B8" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:26" ht="14.25" customHeight="1">
       <c r="A9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="10" spans="1:26" ht="14.25" customHeight="1">
       <c r="A10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11" spans="1:26" ht="14.25" customHeight="1">
       <c r="A11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12" spans="1:26" ht="14.25" customHeight="1">
       <c r="A12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13" spans="1:26" ht="14.25" customHeight="1">
       <c r="A13" t="s">
+        <v>60</v>
+      </c>
+      <c r="B13" t="s">
         <v>61</v>
-      </c>
-      <c r="B13" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="14" spans="1:26" ht="14.25" customHeight="1">
       <c r="A14" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B14" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15" spans="1:26" ht="14.25" customHeight="1">
       <c r="A15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B15" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="16" spans="1:26" ht="14.25" customHeight="1">
       <c r="A16" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B16" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="14.25" customHeight="1">
       <c r="A17" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B17" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="14.25" customHeight="1">
       <c r="A18" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B18" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="14.25" customHeight="1">
       <c r="A19" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B19" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="14.25" customHeight="1">
       <c r="A20" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B20">
         <v>1</v>
